--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/IDAHO_2021.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/IDAHO_2021.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D815"/>
+  <dimension ref="A1:D809"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Asientos</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -434,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C6">
@@ -447,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Mexicali</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Tecate</t>
@@ -504,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -517,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Mulegé</t>
@@ -574,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Carmen</t>
@@ -618,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Champotón</t>
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Escárcega</t>
@@ -644,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Palizada</t>
@@ -657,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Acapetahua</t>
@@ -701,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C25">
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Angel Albino Corzo</t>
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -740,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -753,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Chanal</t>
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Chilón</t>
@@ -779,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C31">
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Copainalá</t>
@@ -805,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Frontera Hidalgo</t>
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Jitotol</t>
@@ -831,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -844,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -857,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C37">
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -883,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Montecristo de Guerrero</t>
+          <t>Montecristo De Guerrero</t>
         </is>
       </c>
       <c r="C39">
@@ -896,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -909,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Ocotepec</t>
@@ -922,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Oxchuc</t>
@@ -935,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Pichucalco</t>
@@ -961,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Salto de Agua</t>
+          <t>Salto De Agua</t>
         </is>
       </c>
       <c r="C45">
@@ -974,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C46">
@@ -987,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -1000,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Solosuchiapa</t>
@@ -1013,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -1026,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Tuxtla Chico</t>
@@ -1039,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -1052,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Tzimol</t>
@@ -1065,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Yajalón</t>
@@ -1078,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1109,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Ascensión</t>
@@ -1122,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Buenaventura</t>
@@ -1135,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Camargo</t>
@@ -1148,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Casas Grandes</t>
@@ -1161,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -1174,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Chínipas</t>
@@ -1187,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1200,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Cusihuiriachi</t>
@@ -1213,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -1226,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -1239,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Guerrero</t>
@@ -1252,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C67">
@@ -1265,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Ignacio Zaragoza</t>
@@ -1278,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -1291,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -1304,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>La Cruz</t>
@@ -1317,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -1330,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Matachí</t>
@@ -1343,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Moris</t>
@@ -1356,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -1369,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -1382,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Rosales</t>
@@ -1395,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -1408,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -1421,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Temósachic</t>
@@ -1434,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1465,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -1478,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -1491,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -1504,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>San Juan de Sabinas</t>
+          <t>San Juan De Sabinas</t>
         </is>
       </c>
       <c r="C86">
@@ -1517,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1530,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1561,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Colima</t>
@@ -1574,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Comala</t>
@@ -1587,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1600,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Ixtlahuacán</t>
@@ -1613,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -1626,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -1639,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1652,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Villa de Álvarez</t>
+          <t>Villa De Álvarez</t>
         </is>
       </c>
       <c r="C97">
@@ -1665,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1680,7 +2125,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1696,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1709,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1722,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1735,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cuajimalpa de Morelos</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C103">
@@ -1748,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1761,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1774,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1787,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1800,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1813,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1826,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1839,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1852,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -1865,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1896,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Cuencamé</t>
@@ -1909,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1922,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -1935,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1948,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1961,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Indé</t>
@@ -1974,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1987,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -2000,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Mezquital</t>
@@ -2013,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Nuevo Ideal</t>
@@ -2026,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Otáez</t>
@@ -2039,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Peñón Blanco</t>
@@ -2052,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Poanas</t>
@@ -2065,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -2078,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Rodeo</t>
@@ -2091,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>San Dimas</t>
@@ -2104,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Santiago Papasquiaro</t>
@@ -2117,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Tamazula</t>
@@ -2130,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Tepehuanes</t>
@@ -2143,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Topia</t>
@@ -2156,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2171,12 +2791,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C136">
@@ -2187,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Aculco</t>
@@ -2200,9 +2825,14 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Almoloya de Alquisiras</t>
+          <t>Almoloya De Alquisiras</t>
         </is>
       </c>
       <c r="C138">
@@ -2213,9 +2843,14 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C139">
@@ -2226,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -2239,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Apaxco</t>
@@ -2252,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Atizapán</t>
@@ -2265,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Atizapán de Zaragoza</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C143">
@@ -2278,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -2291,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -2304,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -2317,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -2330,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Cuautitlán Izcalli</t>
@@ -2343,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Donato Guerra</t>
@@ -2356,9 +3041,14 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C150">
@@ -2369,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Ecatzingo</t>
@@ -2382,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -2395,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Huixquilucan</t>
@@ -2408,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Ixtapaluca</t>
@@ -2421,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C155">
@@ -2434,9 +3149,14 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ixtapan del Oro</t>
+          <t>Ixtapan Del Oro</t>
         </is>
       </c>
       <c r="C156">
@@ -2447,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -2460,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -2473,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -2486,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Malinalco</t>
@@ -2499,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -2512,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C162">
@@ -2525,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -2538,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Nicolás Romero</t>
@@ -2551,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Ocuilan</t>
@@ -2564,9 +3329,14 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C166">
@@ -2577,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Soyaniquilpan de Juárez</t>
+          <t>Soyaniquilpan De Juárez</t>
         </is>
       </c>
       <c r="C167">
@@ -2590,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -2603,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -2616,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -2629,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -2642,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Temoaya</t>
@@ -2655,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -2668,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tenango del Valle</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C174">
@@ -2681,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Teoloyucan</t>
@@ -2694,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Tepotzotlán</t>
@@ -2707,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -2720,9 +3545,14 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C178">
@@ -2733,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -2746,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -2759,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Tultitlán</t>
@@ -2772,9 +3617,14 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Villa de Allende</t>
+          <t>Villa De Allende</t>
         </is>
       </c>
       <c r="C182">
@@ -2785,6 +3635,11 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -2798,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Xonacatlán</t>
@@ -2811,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Zacualpan</t>
@@ -2824,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Zumpahuacán</t>
@@ -2837,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2868,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Acámbaro</t>
@@ -2881,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -2894,9 +3779,14 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C191">
@@ -2907,9 +3797,14 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C192">
@@ -2920,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -2933,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -2946,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Coroneo</t>
@@ -2959,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -2972,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Cuerámaro</t>
@@ -2985,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -2998,9 +3923,14 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C199">
@@ -3011,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -3024,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Huanímaro</t>
@@ -3037,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -3050,9 +3995,14 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Jaral del Progreso</t>
+          <t>Jaral Del Progreso</t>
         </is>
       </c>
       <c r="C203">
@@ -3063,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -3076,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>León</t>
@@ -3089,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -3102,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -3115,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -3128,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -3141,9 +4121,14 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Purísima del Rincón</t>
+          <t>Purísima Del Rincón</t>
         </is>
       </c>
       <c r="C210">
@@ -3154,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -3167,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -3180,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -3193,9 +4193,14 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>San Diego de la Unión</t>
+          <t>San Diego De La Unión</t>
         </is>
       </c>
       <c r="C214">
@@ -3206,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -3219,9 +4229,14 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>San Francisco del Rincón</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C216">
@@ -3232,9 +4247,14 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C217">
@@ -3245,9 +4265,14 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C218">
@@ -3258,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Santiago Maravatío</t>
@@ -3271,9 +4301,14 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C220">
@@ -3284,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Tarandacuao</t>
@@ -3297,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -3310,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -3323,9 +4373,14 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C224">
@@ -3336,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Villagrán</t>
@@ -3349,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Xichú</t>
@@ -3362,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -3375,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3395,7 +4470,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C229">
@@ -3406,9 +4481,14 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C230">
@@ -3419,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -3432,9 +4517,14 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C232">
@@ -3445,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -3458,9 +4553,14 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C234">
@@ -3471,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -3484,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -3497,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Cuautepec</t>
@@ -3510,9 +4625,14 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C238">
@@ -3523,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -3536,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -3549,9 +4679,14 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C241">
@@ -3562,9 +4697,14 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C242">
@@ -3575,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -3588,9 +4733,14 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>La Unión de Isidoro Montes de Oca</t>
+          <t>La Unión De Isidoro Montes De Oca</t>
         </is>
       </c>
       <c r="C244">
@@ -3601,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -3614,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -3627,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Mochitlán</t>
@@ -3640,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -3653,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -3666,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Pedro Ascencio Alquisiras</t>
@@ -3679,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -3692,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Pilcaya</t>
@@ -3705,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -3718,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -3731,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -3744,9 +4949,14 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C256">
@@ -3757,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -3770,9 +4985,14 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C258">
@@ -3783,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -3796,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Tetipac</t>
@@ -3809,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Tlacoachistlahuaca</t>
@@ -3822,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Tlalchapa</t>
@@ -3835,9 +5075,14 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C263">
@@ -3848,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -3861,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -3874,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Xochihuehuetlán</t>
@@ -3887,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Xochistlahuaca</t>
@@ -3900,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -3913,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3944,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -3957,9 +5237,14 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Agua Blanca de Iturbide</t>
+          <t>Agua Blanca De Iturbide</t>
         </is>
       </c>
       <c r="C272">
@@ -3970,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Alfajayucan</t>
@@ -3983,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Apan</t>
@@ -3996,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Atitalaquia</t>
@@ -4009,9 +5309,14 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C276">
@@ -4022,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Chapulhuacán</t>
@@ -4035,9 +5345,14 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Cuautepec de Hinojosa</t>
+          <t>Cuautepec De Hinojosa</t>
         </is>
       </c>
       <c r="C278">
@@ -4048,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -4061,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -4074,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -4087,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Jaltocán</t>
@@ -4100,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Juárez Hidalgo</t>
@@ -4113,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Lolotla</t>
@@ -4126,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -4139,6 +5489,11 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -4152,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>Nicolás Flores</t>
@@ -4165,9 +5525,14 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C288">
@@ -4178,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Pacula</t>
@@ -4191,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>San Agustín Tlaxiaca</t>
@@ -4204,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Tasquillo</t>
@@ -4217,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -4230,9 +5615,14 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Tepeji del Río de Ocampo</t>
+          <t>Tepeji Del Río De Ocampo</t>
         </is>
       </c>
       <c r="C293">
@@ -4243,9 +5633,14 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Tezontepec de Aldama</t>
+          <t>Tezontepec De Aldama</t>
         </is>
       </c>
       <c r="C294">
@@ -4256,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Tianguistengo</t>
@@ -4269,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Tlahuiltepa</t>
@@ -4282,9 +5687,14 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Tula de Allende</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C297">
@@ -4295,9 +5705,14 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C298">
@@ -4308,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Xochiatipan</t>
@@ -4321,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Xochicoatlán</t>
@@ -4334,9 +5759,14 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Zacualtipán de Ángeles</t>
+          <t>Zacualtipán De Ángeles</t>
         </is>
       </c>
       <c r="C301">
@@ -4347,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -4360,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4380,7 +5820,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Acatlán de Juárez</t>
+          <t>Acatlán De Juárez</t>
         </is>
       </c>
       <c r="C304">
@@ -4391,9 +5831,14 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Ahualulco de Mercado</t>
+          <t>Ahualulco De Mercado</t>
         </is>
       </c>
       <c r="C305">
@@ -4404,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Amatitán</t>
@@ -4417,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Arandas</t>
@@ -4430,9 +5885,14 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Atotonilco el Alto</t>
+          <t>Atotonilco El Alto</t>
         </is>
       </c>
       <c r="C308">
@@ -4443,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Atoyac</t>
@@ -4456,9 +5921,14 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C310">
@@ -4469,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Ayotlán</t>
@@ -4482,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -4495,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Cabo Corrientes</t>
@@ -4508,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Casimiro Castillo</t>
@@ -4521,9 +6011,14 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Cañadas de Obregón</t>
+          <t>Cañadas De Obregón</t>
         </is>
       </c>
       <c r="C315">
@@ -4534,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Chapala</t>
@@ -4547,6 +6047,11 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>Cihuatlán</t>
@@ -4560,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -4573,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Colotlán</t>
@@ -4586,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -4599,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>El Arenal</t>
@@ -4612,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>El Grullo</t>
@@ -4625,9 +6155,14 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C323">
@@ -4638,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Etzatlán</t>
@@ -4651,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -4664,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Guachinango</t>
@@ -4677,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -4690,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>Hostotipaquillo</t>
@@ -4703,9 +6263,14 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Huejuquilla el Alto</t>
+          <t>Huejuquilla El Alto</t>
         </is>
       </c>
       <c r="C329">
@@ -4716,9 +6281,14 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Ixtlahuacán del Río</t>
+          <t>Ixtlahuacán Del Río</t>
         </is>
       </c>
       <c r="C330">
@@ -4729,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Jalostotitlán</t>
@@ -4742,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -4755,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Jocotepec</t>
@@ -4768,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Juanacatlán</t>
@@ -4781,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -4794,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -4807,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -4820,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Mazamitla</t>
@@ -4833,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -4846,9 +6461,14 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Ojuelos de Jalisco</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C340">
@@ -4859,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Pihuamo</t>
@@ -4872,6 +6497,11 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
           <t>Poncitlán</t>
@@ -4885,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -4898,9 +6533,14 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>San Cristóbal de la Barranca</t>
+          <t>San Cristóbal De La Barranca</t>
         </is>
       </c>
       <c r="C344">
@@ -4911,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>San Gabriel</t>
@@ -4924,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -4937,9 +6587,14 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>San Martín de Bolaños</t>
+          <t>San Martín De Bolaños</t>
         </is>
       </c>
       <c r="C347">
@@ -4950,6 +6605,11 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>San Martín Hidalgo</t>
@@ -4963,9 +6623,14 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C349">
@@ -4976,9 +6641,14 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>San Sebastián del Oeste</t>
+          <t>San Sebastián Del Oeste</t>
         </is>
       </c>
       <c r="C350">
@@ -4989,6 +6659,11 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
           <t>Sayula</t>
@@ -5002,6 +6677,11 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -5015,9 +6695,14 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Talpa de Allende</t>
+          <t>Talpa De Allende</t>
         </is>
       </c>
       <c r="C353">
@@ -5028,9 +6713,14 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C354">
@@ -5041,6 +6731,11 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Tecalitlán</t>
@@ -5054,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -5067,9 +6767,14 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Teocuitatlán de Corona</t>
+          <t>Teocuitatlán De Corona</t>
         </is>
       </c>
       <c r="C357">
@@ -5080,9 +6785,14 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C358">
@@ -5093,6 +6803,11 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -5106,9 +6821,14 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C360">
@@ -5119,6 +6839,11 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -5132,6 +6857,11 @@
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
           <t>Tolimán</t>
@@ -5145,6 +6875,11 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -5158,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -5171,6 +6911,11 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -5184,9 +6929,14 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Unión de San Antonio</t>
+          <t>Unión De San Antonio</t>
         </is>
       </c>
       <c r="C366">
@@ -5197,9 +6947,14 @@
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C367">
@@ -5210,9 +6965,14 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Valle de Guadalupe</t>
+          <t>Valle De Guadalupe</t>
         </is>
       </c>
       <c r="C368">
@@ -5223,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>Villa Corona</t>
@@ -5236,6 +7001,11 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -5249,9 +7019,14 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Yahualica de González Gallo</t>
+          <t>Yahualica De González Gallo</t>
         </is>
       </c>
       <c r="C371">
@@ -5262,9 +7037,14 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Zacoalco de Torres</t>
+          <t>Zacoalco De Torres</t>
         </is>
       </c>
       <c r="C372">
@@ -5275,6 +7055,11 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -5288,6 +7073,11 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
           <t>Zapotiltic</t>
@@ -5301,9 +7091,14 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Zapotitlán de Vadillo</t>
+          <t>Zapotitlán De Vadillo</t>
         </is>
       </c>
       <c r="C375">
@@ -5314,9 +7109,14 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C376">
@@ -5327,6 +7127,11 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -5340,6 +7145,11 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5371,6 +7181,11 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
           <t>Aguililla</t>
@@ -5384,6 +7199,11 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
           <t>Álvaro Obregón</t>
@@ -5397,6 +7217,11 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>Angamacutiro</t>
@@ -5410,6 +7235,11 @@
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -5423,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>Aporo</t>
@@ -5436,6 +7271,11 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
           <t>Aquila</t>
@@ -5449,6 +7289,11 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -5462,6 +7307,11 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>Arteaga</t>
@@ -5475,6 +7325,11 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
           <t>Buenavista</t>
@@ -5488,6 +7343,11 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
           <t>Carácuaro</t>
@@ -5501,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>Charapan</t>
@@ -5514,6 +7379,11 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
           <t>Charo</t>
@@ -5527,6 +7397,11 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>Cherán</t>
@@ -5540,6 +7415,11 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
           <t>Chilchota</t>
@@ -5553,6 +7433,11 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>Chucándiro</t>
@@ -5566,6 +7451,11 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
           <t>Churumuco</t>
@@ -5579,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>Coahuayana</t>
@@ -5592,9 +7487,14 @@
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Coalcomán de Vázquez Pallares</t>
+          <t>Coalcomán De Vázquez Pallares</t>
         </is>
       </c>
       <c r="C397">
@@ -5605,6 +7505,11 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -5618,9 +7523,14 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Cojumatlán de Régules</t>
+          <t>Cojumatlán De Régules</t>
         </is>
       </c>
       <c r="C399">
@@ -5631,6 +7541,11 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -5644,6 +7559,11 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>Copándaro</t>
@@ -5657,6 +7577,11 @@
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
           <t>Epitacio Huerta</t>
@@ -5670,6 +7595,11 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
           <t>Erongarícuaro</t>
@@ -5683,6 +7613,11 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
           <t>Gabriel Zamora</t>
@@ -5696,6 +7631,11 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -5709,6 +7649,11 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
           <t>Huandacareo</t>
@@ -5722,6 +7667,11 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>Huaniqueo</t>
@@ -5735,6 +7685,11 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -5748,6 +7703,11 @@
       </c>
     </row>
     <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B409" t="inlineStr">
         <is>
           <t>Indaparapeo</t>
@@ -5761,6 +7721,11 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
           <t>Jacona</t>
@@ -5774,6 +7739,11 @@
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -5787,6 +7757,11 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
           <t>Jiquilpan</t>
@@ -5800,6 +7775,11 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
           <t>José Sixto Verduzco</t>
@@ -5813,6 +7793,11 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
           <t>Jungapeo</t>
@@ -5826,6 +7811,11 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -5839,6 +7829,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -5852,6 +7847,11 @@
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -5865,6 +7865,11 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -5878,6 +7883,11 @@
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
           <t>Madero</t>
@@ -5891,6 +7901,11 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -5904,6 +7919,11 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -5917,6 +7937,11 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -5930,6 +7955,11 @@
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -5943,6 +7973,11 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
           <t>Nocupétaro</t>
@@ -5956,6 +7991,11 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
           <t>Nuevo Parangaricutiro</t>
@@ -5969,6 +8009,11 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
           <t>Nuevo Urecho</t>
@@ -5982,6 +8027,11 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
           <t>Numarán</t>
@@ -5995,6 +8045,11 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -6008,6 +8063,11 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>Pajacuarán</t>
@@ -6021,6 +8081,11 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
           <t>Panindícuaro</t>
@@ -6034,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>Paracho</t>
@@ -6047,6 +8117,11 @@
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
           <t>Parácuaro</t>
@@ -6060,6 +8135,11 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -6073,6 +8153,11 @@
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
           <t>Penjamillo</t>
@@ -6086,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>Peribán</t>
@@ -6099,6 +8189,11 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -6112,6 +8207,11 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
           <t>Queréndaro</t>
@@ -6125,6 +8225,11 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
           <t>Quiroga</t>
@@ -6138,6 +8243,11 @@
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -6151,6 +8261,11 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
           <t>Salvador Escalante</t>
@@ -6164,6 +8279,11 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
           <t>Santa Ana Maya</t>
@@ -6177,6 +8297,11 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
           <t>Senguio</t>
@@ -6190,6 +8315,11 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -6203,6 +8333,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
           <t>Tancítaro</t>
@@ -6216,6 +8351,11 @@
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -6229,6 +8369,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
           <t>Tangancícuaro</t>
@@ -6242,6 +8387,11 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
           <t>Tanhuato</t>
@@ -6255,6 +8405,11 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
           <t>Taretan</t>
@@ -6268,6 +8423,11 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>Tepalcatepec</t>
@@ -6281,6 +8441,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Tingüindín</t>
@@ -6294,6 +8459,11 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
           <t>Tlalpujahua</t>
@@ -6307,6 +8477,11 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
           <t>Tlazazalca</t>
@@ -6320,6 +8495,11 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
           <t>Tumbiscatío</t>
@@ -6333,6 +8513,11 @@
       </c>
     </row>
     <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -6346,6 +8531,11 @@
       </c>
     </row>
     <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B455" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -6359,6 +8549,11 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -6372,6 +8567,11 @@
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
           <t>Tzitzio</t>
@@ -6385,6 +8585,11 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -6398,6 +8603,11 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -6411,6 +8621,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Vista Hermosa</t>
@@ -6424,6 +8639,11 @@
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
           <t>Yurécuaro</t>
@@ -6437,6 +8657,11 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -6450,6 +8675,11 @@
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -6463,6 +8693,11 @@
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
           <t>Zináparo</t>
@@ -6476,6 +8711,11 @@
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -6489,6 +8729,11 @@
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
           <t>Ziracuaretiro</t>
@@ -6502,6 +8747,11 @@
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -6515,6 +8765,11 @@
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6546,6 +8801,11 @@
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
           <t>Axochiapan</t>
@@ -6559,6 +8819,11 @@
       </c>
     </row>
     <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -6572,6 +8837,11 @@
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -6585,6 +8855,11 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -6598,6 +8873,11 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
           <t>Huitzilac</t>
@@ -6611,6 +8891,11 @@
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
           <t>Jiutepec</t>
@@ -6624,6 +8909,11 @@
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -6637,6 +8927,11 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -6650,6 +8945,11 @@
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
           <t>Temoac</t>
@@ -6663,6 +8963,11 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
           <t>Tepoztlán</t>
@@ -6676,6 +8981,11 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Tetecala</t>
@@ -6689,9 +8999,14 @@
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Tlaltizapán de Zapata</t>
+          <t>Tlaltizapán De Zapata</t>
         </is>
       </c>
       <c r="C481">
@@ -6702,6 +9017,11 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -6715,6 +9035,11 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
           <t>Tlayacapan</t>
@@ -6728,6 +9053,11 @@
       </c>
     </row>
     <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr">
         <is>
           <t>Totolapan</t>
@@ -6741,6 +9071,11 @@
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -6754,6 +9089,11 @@
       </c>
     </row>
     <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B486" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6785,6 +9125,11 @@
       </c>
     </row>
     <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B488" t="inlineStr">
         <is>
           <t>Ahuacatlán</t>
@@ -6798,9 +9143,14 @@
       </c>
     </row>
     <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Amatlán de Cañas</t>
+          <t>Amatlán De Cañas</t>
         </is>
       </c>
       <c r="C489">
@@ -6811,9 +9161,14 @@
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Bahía de Banderas</t>
+          <t>Bahía De Banderas</t>
         </is>
       </c>
       <c r="C490">
@@ -6824,6 +9179,11 @@
       </c>
     </row>
     <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B491" t="inlineStr">
         <is>
           <t>Compostela</t>
@@ -6837,6 +9197,11 @@
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
           <t>Del Nayar</t>
@@ -6850,6 +9215,11 @@
       </c>
     </row>
     <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B493" t="inlineStr">
         <is>
           <t>Huajicori</t>
@@ -6863,9 +9233,14 @@
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Ixtlán del Río</t>
+          <t>Ixtlán Del Río</t>
         </is>
       </c>
       <c r="C494">
@@ -6876,6 +9251,11 @@
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
           <t>Jala</t>
@@ -6889,6 +9269,11 @@
       </c>
     </row>
     <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B496" t="inlineStr">
         <is>
           <t>La Yesca</t>
@@ -6902,6 +9287,11 @@
       </c>
     </row>
     <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B497" t="inlineStr">
         <is>
           <t>Rosamorada</t>
@@ -6915,6 +9305,11 @@
       </c>
     </row>
     <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B498" t="inlineStr">
         <is>
           <t>Ruíz</t>
@@ -6928,6 +9323,11 @@
       </c>
     </row>
     <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B499" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -6941,6 +9341,11 @@
       </c>
     </row>
     <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
           <t>San Pedro Lagunillas</t>
@@ -6954,9 +9359,14 @@
       </c>
     </row>
     <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Santa María del Oro</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C501">
@@ -6967,6 +9377,11 @@
       </c>
     </row>
     <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B502" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -6980,6 +9395,11 @@
       </c>
     </row>
     <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B503" t="inlineStr">
         <is>
           <t>Tecuala</t>
@@ -6993,6 +9413,11 @@
       </c>
     </row>
     <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B504" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -7006,6 +9431,11 @@
       </c>
     </row>
     <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B505" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -7019,6 +9449,11 @@
       </c>
     </row>
     <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B506" t="inlineStr">
         <is>
           <t>Xalisco</t>
@@ -7032,6 +9467,11 @@
       </c>
     </row>
     <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B507" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7063,6 +9503,11 @@
       </c>
     </row>
     <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B509" t="inlineStr">
         <is>
           <t>Galeana</t>
@@ -7076,6 +9521,11 @@
       </c>
     </row>
     <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B510" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -7089,6 +9539,11 @@
       </c>
     </row>
     <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B511" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -7102,9 +9557,14 @@
       </c>
     </row>
     <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C512">
@@ -7115,6 +9575,11 @@
       </c>
     </row>
     <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B513" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7146,6 +9611,11 @@
       </c>
     </row>
     <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B515" t="inlineStr">
         <is>
           <t>Coatecas Altas</t>
@@ -7159,9 +9629,14 @@
       </c>
     </row>
     <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Coicoyán de las Flores</t>
+          <t>Coicoyán De Las Flores</t>
         </is>
       </c>
       <c r="C516">
@@ -7172,9 +9647,14 @@
       </c>
     </row>
     <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Constancia del Rosario</t>
+          <t>Constancia Del Rosario</t>
         </is>
       </c>
       <c r="C517">
@@ -7185,9 +9665,14 @@
       </c>
     </row>
     <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C518">
@@ -7198,9 +9683,14 @@
       </c>
     </row>
     <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Tlaxiaco</t>
+          <t>Heroica Ciudad De Tlaxiaco</t>
         </is>
       </c>
       <c r="C519">
@@ -7211,9 +9701,14 @@
       </c>
     </row>
     <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C520">
@@ -7224,6 +9719,11 @@
       </c>
     </row>
     <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B521" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -7237,9 +9737,14 @@
       </c>
     </row>
     <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C522">
@@ -7250,9 +9755,14 @@
       </c>
     </row>
     <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Nejapa de Madero</t>
+          <t>Nejapa De Madero</t>
         </is>
       </c>
       <c r="C523">
@@ -7263,9 +9773,14 @@
       </c>
     </row>
     <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C524">
@@ -7276,9 +9791,14 @@
       </c>
     </row>
     <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C525">
@@ -7289,6 +9809,11 @@
       </c>
     </row>
     <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B526" t="inlineStr">
         <is>
           <t>Pluma Hidalgo</t>
@@ -7302,6 +9827,11 @@
       </c>
     </row>
     <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B527" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -7315,6 +9845,11 @@
       </c>
     </row>
     <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B528" t="inlineStr">
         <is>
           <t>San Antonio Huitepec</t>
@@ -7328,6 +9863,11 @@
       </c>
     </row>
     <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B529" t="inlineStr">
         <is>
           <t>San Francisco Sola</t>
@@ -7341,6 +9881,11 @@
       </c>
     </row>
     <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B530" t="inlineStr">
         <is>
           <t>San Ildefonso Sola</t>
@@ -7354,6 +9899,11 @@
       </c>
     </row>
     <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B531" t="inlineStr">
         <is>
           <t>San José Chiltepec</t>
@@ -7367,6 +9917,11 @@
       </c>
     </row>
     <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B532" t="inlineStr">
         <is>
           <t>San Juan Bautista Cuicatlán</t>
@@ -7380,6 +9935,11 @@
       </c>
     </row>
     <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B533" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -7393,6 +9953,11 @@
       </c>
     </row>
     <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B534" t="inlineStr">
         <is>
           <t>San Juan Bautista Valle Nacional</t>
@@ -7406,6 +9971,11 @@
       </c>
     </row>
     <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B535" t="inlineStr">
         <is>
           <t>San Juan Cacahuatepec</t>
@@ -7419,6 +9989,11 @@
       </c>
     </row>
     <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B536" t="inlineStr">
         <is>
           <t>San Juan Cotzocón</t>
@@ -7432,6 +10007,11 @@
       </c>
     </row>
     <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B537" t="inlineStr">
         <is>
           <t>San Juan Mixtepec - Distr. 08 -</t>
@@ -7445,6 +10025,11 @@
       </c>
     </row>
     <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B538" t="inlineStr">
         <is>
           <t>San Juan Teitipac</t>
@@ -7458,6 +10043,11 @@
       </c>
     </row>
     <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B539" t="inlineStr">
         <is>
           <t>San Lorenzo Cacaotepec</t>
@@ -7471,6 +10061,11 @@
       </c>
     </row>
     <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B540" t="inlineStr">
         <is>
           <t>San Martín Itunyoso</t>
@@ -7484,6 +10079,11 @@
       </c>
     </row>
     <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B541" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -7497,6 +10097,11 @@
       </c>
     </row>
     <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B542" t="inlineStr">
         <is>
           <t>San Mateo Piñas</t>
@@ -7510,6 +10115,11 @@
       </c>
     </row>
     <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B543" t="inlineStr">
         <is>
           <t>San Miguel Tecomatlán</t>
@@ -7523,6 +10133,11 @@
       </c>
     </row>
     <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B544" t="inlineStr">
         <is>
           <t>San Pablo Cuatro Venados</t>
@@ -7536,6 +10151,11 @@
       </c>
     </row>
     <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B545" t="inlineStr">
         <is>
           <t>San Pedro Amuzgos</t>
@@ -7549,6 +10169,11 @@
       </c>
     </row>
     <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B546" t="inlineStr">
         <is>
           <t>San Pedro Mixtepec - Distr. 22 -</t>
@@ -7562,6 +10187,11 @@
       </c>
     </row>
     <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B547" t="inlineStr">
         <is>
           <t>San Pedro Quiatoni</t>
@@ -7575,6 +10205,11 @@
       </c>
     </row>
     <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B548" t="inlineStr">
         <is>
           <t>San Pedro Tapanatepec</t>
@@ -7588,6 +10223,11 @@
       </c>
     </row>
     <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B549" t="inlineStr">
         <is>
           <t>San Sebastián Ixcapa</t>
@@ -7601,6 +10241,11 @@
       </c>
     </row>
     <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B550" t="inlineStr">
         <is>
           <t>Santa Catarina Ixtepeji</t>
@@ -7614,6 +10259,11 @@
       </c>
     </row>
     <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B551" t="inlineStr">
         <is>
           <t>Santa Cruz Tayata</t>
@@ -7627,6 +10277,11 @@
       </c>
     </row>
     <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B552" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -7640,6 +10295,11 @@
       </c>
     </row>
     <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B553" t="inlineStr">
         <is>
           <t>Santa Lucía Ocotlán</t>
@@ -7653,6 +10313,11 @@
       </c>
     </row>
     <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B554" t="inlineStr">
         <is>
           <t>Santa María Guienagati</t>
@@ -7666,6 +10331,11 @@
       </c>
     </row>
     <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B555" t="inlineStr">
         <is>
           <t>Santa María Huatulco</t>
@@ -7679,6 +10349,11 @@
       </c>
     </row>
     <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B556" t="inlineStr">
         <is>
           <t>Santa María Peñoles</t>
@@ -7692,6 +10367,11 @@
       </c>
     </row>
     <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B557" t="inlineStr">
         <is>
           <t>Santa María Tlahuitoltepec</t>
@@ -7705,6 +10385,11 @@
       </c>
     </row>
     <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B558" t="inlineStr">
         <is>
           <t>Santa María Tonameca</t>
@@ -7718,6 +10403,11 @@
       </c>
     </row>
     <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B559" t="inlineStr">
         <is>
           <t>Santiago Amoltepec</t>
@@ -7731,6 +10421,11 @@
       </c>
     </row>
     <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B560" t="inlineStr">
         <is>
           <t>Santiago Choápam</t>
@@ -7744,6 +10439,11 @@
       </c>
     </row>
     <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B561" t="inlineStr">
         <is>
           <t>Santiago Ixtayutla</t>
@@ -7757,6 +10457,11 @@
       </c>
     </row>
     <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B562" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -7770,6 +10475,11 @@
       </c>
     </row>
     <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B563" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -7783,6 +10493,11 @@
       </c>
     </row>
     <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B564" t="inlineStr">
         <is>
           <t>Santiago Nuyoó</t>
@@ -7796,6 +10511,11 @@
       </c>
     </row>
     <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B565" t="inlineStr">
         <is>
           <t>Santiago Tetepec</t>
@@ -7809,6 +10529,11 @@
       </c>
     </row>
     <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B566" t="inlineStr">
         <is>
           <t>Santiago Tilantongo</t>
@@ -7822,6 +10547,11 @@
       </c>
     </row>
     <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B567" t="inlineStr">
         <is>
           <t>Santo Domingo Tehuantepec</t>
@@ -7835,6 +10565,11 @@
       </c>
     </row>
     <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B568" t="inlineStr">
         <is>
           <t>Santo Domingo Tonalá</t>
@@ -7848,6 +10583,11 @@
       </c>
     </row>
     <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B569" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -7861,6 +10601,11 @@
       </c>
     </row>
     <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B570" t="inlineStr">
         <is>
           <t>Santos Reyes Pápalo</t>
@@ -7874,6 +10619,11 @@
       </c>
     </row>
     <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B571" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -7887,9 +10637,14 @@
       </c>
     </row>
     <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Tataltepec de Valdés</t>
+          <t>Tataltepec De Valdés</t>
         </is>
       </c>
       <c r="C572">
@@ -7900,9 +10655,14 @@
       </c>
     </row>
     <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Teotitlán de Flores Magón</t>
+          <t>Teotitlán De Flores Magón</t>
         </is>
       </c>
       <c r="C573">
@@ -7913,9 +10673,14 @@
       </c>
     </row>
     <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Tezoatlán de Segura y Luna</t>
+          <t>Tezoatlán De Segura Y Luna</t>
         </is>
       </c>
       <c r="C574">
@@ -7926,9 +10691,14 @@
       </c>
     </row>
     <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C575">
@@ -7939,9 +10709,14 @@
       </c>
     </row>
     <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Totontepec Villa de Morelos</t>
+          <t>Totontepec Villa De Morelos</t>
         </is>
       </c>
       <c r="C576">
@@ -7952,9 +10727,14 @@
       </c>
     </row>
     <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Villa de Tututepec de Melchor Ocampo</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C577">
@@ -7965,9 +10745,14 @@
       </c>
     </row>
     <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Zapotitlán del Río</t>
+          <t>Zapotitlán Del Río</t>
         </is>
       </c>
       <c r="C578">
@@ -7978,9 +10763,14 @@
       </c>
     </row>
     <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C579">
@@ -7991,6 +10781,11 @@
       </c>
     </row>
     <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B580" t="inlineStr">
         <is>
           <t>Total</t>
@@ -8022,6 +10817,11 @@
       </c>
     </row>
     <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B582" t="inlineStr">
         <is>
           <t>Acatlán</t>
@@ -8035,6 +10835,11 @@
       </c>
     </row>
     <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B583" t="inlineStr">
         <is>
           <t>Acatzingo</t>
@@ -8048,6 +10853,11 @@
       </c>
     </row>
     <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B584" t="inlineStr">
         <is>
           <t>Aquixtla</t>
@@ -8061,6 +10871,11 @@
       </c>
     </row>
     <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B585" t="inlineStr">
         <is>
           <t>Atexcal</t>
@@ -8074,6 +10889,11 @@
       </c>
     </row>
     <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B586" t="inlineStr">
         <is>
           <t>Cañada Morelos</t>
@@ -8087,6 +10907,11 @@
       </c>
     </row>
     <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B587" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -8100,6 +10925,11 @@
       </c>
     </row>
     <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B588" t="inlineStr">
         <is>
           <t>Chiautzingo</t>
@@ -8113,6 +10943,11 @@
       </c>
     </row>
     <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B589" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -8126,6 +10961,11 @@
       </c>
     </row>
     <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B590" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -8139,6 +10979,11 @@
       </c>
     </row>
     <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B591" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -8152,6 +10997,11 @@
       </c>
     </row>
     <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B592" t="inlineStr">
         <is>
           <t>Coxcatlán</t>
@@ -8165,6 +11015,11 @@
       </c>
     </row>
     <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B593" t="inlineStr">
         <is>
           <t>Esperanza</t>
@@ -8178,6 +11033,11 @@
       </c>
     </row>
     <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B594" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -8191,6 +11051,11 @@
       </c>
     </row>
     <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B595" t="inlineStr">
         <is>
           <t>Huatlatlauca</t>
@@ -8204,9 +11069,14 @@
       </c>
     </row>
     <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C596">
@@ -8217,6 +11087,11 @@
       </c>
     </row>
     <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B597" t="inlineStr">
         <is>
           <t>Jalpan</t>
@@ -8230,6 +11105,11 @@
       </c>
     </row>
     <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B598" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -8243,6 +11123,11 @@
       </c>
     </row>
     <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B599" t="inlineStr">
         <is>
           <t>Nopalucan</t>
@@ -8256,6 +11141,11 @@
       </c>
     </row>
     <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B600" t="inlineStr">
         <is>
           <t>Ocoyucan</t>
@@ -8269,9 +11159,14 @@
       </c>
     </row>
     <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Palmar de Bravo</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C601">
@@ -8282,6 +11177,11 @@
       </c>
     </row>
     <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B602" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -8295,6 +11195,11 @@
       </c>
     </row>
     <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B603" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -8308,6 +11213,11 @@
       </c>
     </row>
     <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B604" t="inlineStr">
         <is>
           <t>San Antonio Cañada</t>
@@ -8321,6 +11231,11 @@
       </c>
     </row>
     <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B605" t="inlineStr">
         <is>
           <t>San Felipe Teotlalcingo</t>
@@ -8334,9 +11249,14 @@
       </c>
     </row>
     <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>San Salvador el Seco</t>
+          <t>San Salvador El Seco</t>
         </is>
       </c>
       <c r="C606">
@@ -8347,6 +11267,11 @@
       </c>
     </row>
     <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B607" t="inlineStr">
         <is>
           <t>Santa Inés Ahuatempan</t>
@@ -8360,6 +11285,11 @@
       </c>
     </row>
     <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B608" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -8373,6 +11303,11 @@
       </c>
     </row>
     <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B609" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -8386,6 +11321,11 @@
       </c>
     </row>
     <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B610" t="inlineStr">
         <is>
           <t>Tenampulco</t>
@@ -8399,6 +11339,11 @@
       </c>
     </row>
     <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B611" t="inlineStr">
         <is>
           <t>Teopantlán</t>
@@ -8412,6 +11357,11 @@
       </c>
     </row>
     <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B612" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -8425,9 +11375,14 @@
       </c>
     </row>
     <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C613">
@@ -8438,6 +11393,11 @@
       </c>
     </row>
     <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B614" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -8451,9 +11411,14 @@
       </c>
     </row>
     <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C615">
@@ -8464,6 +11429,11 @@
       </c>
     </row>
     <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B616" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -8477,6 +11447,11 @@
       </c>
     </row>
     <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B617" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -8490,6 +11465,11 @@
       </c>
     </row>
     <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B618" t="inlineStr">
         <is>
           <t>Tzicatlacoyan</t>
@@ -8503,6 +11483,11 @@
       </c>
     </row>
     <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B619" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -8516,6 +11501,11 @@
       </c>
     </row>
     <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B620" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -8529,6 +11519,11 @@
       </c>
     </row>
     <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B621" t="inlineStr">
         <is>
           <t>Xiutetelco</t>
@@ -8542,6 +11537,11 @@
       </c>
     </row>
     <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B622" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -8555,6 +11555,11 @@
       </c>
     </row>
     <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B623" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -8568,6 +11573,11 @@
       </c>
     </row>
     <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B624" t="inlineStr">
         <is>
           <t>Zinacatepec</t>
@@ -8581,6 +11591,11 @@
       </c>
     </row>
     <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B625" t="inlineStr">
         <is>
           <t>Total</t>
@@ -8601,7 +11616,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C626">
@@ -8612,6 +11627,11 @@
       </c>
     </row>
     <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B627" t="inlineStr">
         <is>
           <t>Arroyo Seco</t>
@@ -8625,9 +11645,14 @@
       </c>
     </row>
     <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C628">
@@ -8638,6 +11663,11 @@
       </c>
     </row>
     <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B629" t="inlineStr">
         <is>
           <t>El Marqués</t>
@@ -8651,6 +11681,11 @@
       </c>
     </row>
     <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B630" t="inlineStr">
         <is>
           <t>Ezequiel Montes</t>
@@ -8664,9 +11699,14 @@
       </c>
     </row>
     <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C631">
@@ -8677,9 +11717,14 @@
       </c>
     </row>
     <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C632">
@@ -8690,6 +11735,11 @@
       </c>
     </row>
     <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B633" t="inlineStr">
         <is>
           <t>Peñamiller</t>
@@ -8703,9 +11753,14 @@
       </c>
     </row>
     <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C634">
@@ -8716,6 +11771,11 @@
       </c>
     </row>
     <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B635" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -8729,6 +11789,11 @@
       </c>
     </row>
     <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B636" t="inlineStr">
         <is>
           <t>San Joaquín</t>
@@ -8742,9 +11807,14 @@
       </c>
     </row>
     <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C637">
@@ -8755,6 +11825,11 @@
       </c>
     </row>
     <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B638" t="inlineStr">
         <is>
           <t>Total</t>
@@ -8786,6 +11861,11 @@
       </c>
     </row>
     <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B640" t="inlineStr">
         <is>
           <t>Alaquines</t>
@@ -8799,9 +11879,14 @@
       </c>
     </row>
     <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Armadillo de los Infante</t>
+          <t>Armadillo De Los Infante</t>
         </is>
       </c>
       <c r="C641">
@@ -8812,6 +11897,11 @@
       </c>
     </row>
     <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B642" t="inlineStr">
         <is>
           <t>Charcas</t>
@@ -8825,9 +11915,14 @@
       </c>
     </row>
     <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C643">
@@ -8838,6 +11933,11 @@
       </c>
     </row>
     <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B644" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -8851,9 +11951,14 @@
       </c>
     </row>
     <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Mexquitic de Carmona</t>
+          <t>Mexquitic De Carmona</t>
         </is>
       </c>
       <c r="C645">
@@ -8864,6 +11969,11 @@
       </c>
     </row>
     <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B646" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -8877,6 +11987,11 @@
       </c>
     </row>
     <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B647" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -8890,6 +12005,11 @@
       </c>
     </row>
     <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B648" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -8903,9 +12023,14 @@
       </c>
     </row>
     <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Soledad de Graciano Sánchez</t>
+          <t>Soledad De Graciano Sánchez</t>
         </is>
       </c>
       <c r="C649">
@@ -8916,6 +12041,11 @@
       </c>
     </row>
     <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B650" t="inlineStr">
         <is>
           <t>Tamazunchale</t>
@@ -8929,6 +12059,11 @@
       </c>
     </row>
     <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B651" t="inlineStr">
         <is>
           <t>Venado</t>
@@ -8942,9 +12077,14 @@
       </c>
     </row>
     <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Villa de Guadalupe</t>
+          <t>Villa De Guadalupe</t>
         </is>
       </c>
       <c r="C652">
@@ -8955,9 +12095,14 @@
       </c>
     </row>
     <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C653">
@@ -8968,9 +12113,14 @@
       </c>
     </row>
     <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Villa de Reyes</t>
+          <t>Villa De Reyes</t>
         </is>
       </c>
       <c r="C654">
@@ -8981,6 +12131,11 @@
       </c>
     </row>
     <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B655" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -8994,6 +12149,11 @@
       </c>
     </row>
     <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B656" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9025,6 +12185,11 @@
       </c>
     </row>
     <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B658" t="inlineStr">
         <is>
           <t>Angostura</t>
@@ -9038,6 +12203,11 @@
       </c>
     </row>
     <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B659" t="inlineStr">
         <is>
           <t>Badiraguato</t>
@@ -9051,6 +12221,11 @@
       </c>
     </row>
     <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B660" t="inlineStr">
         <is>
           <t>Choix</t>
@@ -9064,6 +12239,11 @@
       </c>
     </row>
     <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B661" t="inlineStr">
         <is>
           <t>Cosalá</t>
@@ -9077,6 +12257,11 @@
       </c>
     </row>
     <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B662" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -9086,10 +12271,15 @@
         <v>41</v>
       </c>
       <c r="D662">
-        <v>0.009414466130884041</v>
+        <v>0.00941446613088404</v>
       </c>
     </row>
     <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B663" t="inlineStr">
         <is>
           <t>El Fuerte</t>
@@ -9103,6 +12293,11 @@
       </c>
     </row>
     <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B664" t="inlineStr">
         <is>
           <t>Elota</t>
@@ -9116,6 +12311,11 @@
       </c>
     </row>
     <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B665" t="inlineStr">
         <is>
           <t>Escuinapa</t>
@@ -9129,6 +12329,11 @@
       </c>
     </row>
     <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B666" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -9142,6 +12347,11 @@
       </c>
     </row>
     <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B667" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -9155,6 +12365,11 @@
       </c>
     </row>
     <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B668" t="inlineStr">
         <is>
           <t>Mocorito</t>
@@ -9168,6 +12383,11 @@
       </c>
     </row>
     <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B669" t="inlineStr">
         <is>
           <t>Navolato</t>
@@ -9181,6 +12401,11 @@
       </c>
     </row>
     <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B670" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -9194,6 +12419,11 @@
       </c>
     </row>
     <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B671" t="inlineStr">
         <is>
           <t>Salvador Alvarado</t>
@@ -9207,6 +12437,11 @@
       </c>
     </row>
     <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B672" t="inlineStr">
         <is>
           <t>San Ignacio</t>
@@ -9220,6 +12455,11 @@
       </c>
     </row>
     <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B673" t="inlineStr">
         <is>
           <t>Sinaloa</t>
@@ -9233,6 +12473,11 @@
       </c>
     </row>
     <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B674" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9264,6 +12509,11 @@
       </c>
     </row>
     <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B676" t="inlineStr">
         <is>
           <t>Bácum</t>
@@ -9277,6 +12527,11 @@
       </c>
     </row>
     <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B677" t="inlineStr">
         <is>
           <t>Caborca</t>
@@ -9290,6 +12545,11 @@
       </c>
     </row>
     <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B678" t="inlineStr">
         <is>
           <t>Cajeme</t>
@@ -9303,6 +12563,11 @@
       </c>
     </row>
     <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B679" t="inlineStr">
         <is>
           <t>Empalme</t>
@@ -9316,6 +12581,11 @@
       </c>
     </row>
     <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B680" t="inlineStr">
         <is>
           <t>Etchojoa</t>
@@ -9329,6 +12599,11 @@
       </c>
     </row>
     <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B681" t="inlineStr">
         <is>
           <t>Fronteras</t>
@@ -9342,6 +12617,11 @@
       </c>
     </row>
     <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B682" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -9355,6 +12635,11 @@
       </c>
     </row>
     <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B683" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -9368,6 +12653,11 @@
       </c>
     </row>
     <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B684" t="inlineStr">
         <is>
           <t>Huatabampo</t>
@@ -9381,6 +12671,11 @@
       </c>
     </row>
     <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B685" t="inlineStr">
         <is>
           <t>Imuris</t>
@@ -9394,6 +12689,11 @@
       </c>
     </row>
     <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B686" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -9407,9 +12707,14 @@
       </c>
     </row>
     <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Nacozari de García</t>
+          <t>Nacozari De García</t>
         </is>
       </c>
       <c r="C687">
@@ -9420,6 +12725,11 @@
       </c>
     </row>
     <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B688" t="inlineStr">
         <is>
           <t>Navojoa</t>
@@ -9433,6 +12743,11 @@
       </c>
     </row>
     <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B689" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -9446,6 +12761,11 @@
       </c>
     </row>
     <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B690" t="inlineStr">
         <is>
           <t>Puerto Peñasco</t>
@@ -9459,6 +12779,11 @@
       </c>
     </row>
     <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B691" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -9472,6 +12797,11 @@
       </c>
     </row>
     <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B692" t="inlineStr">
         <is>
           <t>Sahuaripa</t>
@@ -9485,6 +12815,11 @@
       </c>
     </row>
     <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B693" t="inlineStr">
         <is>
           <t>San Luis Río Colorado</t>
@@ -9498,6 +12833,11 @@
       </c>
     </row>
     <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B694" t="inlineStr">
         <is>
           <t>Yécora</t>
@@ -9511,6 +12851,11 @@
       </c>
     </row>
     <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B695" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9542,6 +12887,11 @@
       </c>
     </row>
     <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B697" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -9555,6 +12905,11 @@
       </c>
     </row>
     <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B698" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -9568,6 +12923,11 @@
       </c>
     </row>
     <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B699" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -9581,6 +12941,11 @@
       </c>
     </row>
     <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B700" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9612,6 +12977,11 @@
       </c>
     </row>
     <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B702" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -9625,6 +12995,11 @@
       </c>
     </row>
     <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B703" t="inlineStr">
         <is>
           <t>González</t>
@@ -9638,6 +13013,11 @@
       </c>
     </row>
     <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B704" t="inlineStr">
         <is>
           <t>Gustavo Díaz Ordaz</t>
@@ -9651,6 +13031,11 @@
       </c>
     </row>
     <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B705" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -9664,6 +13049,11 @@
       </c>
     </row>
     <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B706" t="inlineStr">
         <is>
           <t>Nuevo Laredo</t>
@@ -9677,6 +13067,11 @@
       </c>
     </row>
     <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B707" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -9690,6 +13085,11 @@
       </c>
     </row>
     <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B708" t="inlineStr">
         <is>
           <t>Río Bravo</t>
@@ -9703,6 +13103,11 @@
       </c>
     </row>
     <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B709" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -9716,6 +13121,11 @@
       </c>
     </row>
     <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B710" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9747,6 +13157,11 @@
       </c>
     </row>
     <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B712" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -9760,6 +13175,11 @@
       </c>
     </row>
     <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B713" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -9773,6 +13193,11 @@
       </c>
     </row>
     <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B714" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -9786,9 +13211,14 @@
       </c>
     </row>
     <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Ixtacuixtla de Mariano Matamoros</t>
+          <t>Ixtacuixtla De Mariano Matamoros</t>
         </is>
       </c>
       <c r="C715">
@@ -9799,6 +13229,11 @@
       </c>
     </row>
     <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B716" t="inlineStr">
         <is>
           <t>Natívitas</t>
@@ -9812,6 +13247,11 @@
       </c>
     </row>
     <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B717" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -9825,6 +13265,11 @@
       </c>
     </row>
     <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B718" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -9838,6 +13283,11 @@
       </c>
     </row>
     <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B719" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -9851,6 +13301,11 @@
       </c>
     </row>
     <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B720" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -9864,6 +13319,11 @@
       </c>
     </row>
     <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B721" t="inlineStr">
         <is>
           <t>Zacatelco</t>
@@ -9877,6 +13337,11 @@
       </c>
     </row>
     <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B722" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9908,6 +13373,11 @@
       </c>
     </row>
     <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B724" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -9921,6 +13391,11 @@
       </c>
     </row>
     <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B725" t="inlineStr">
         <is>
           <t>Acultzingo</t>
@@ -9934,6 +13409,11 @@
       </c>
     </row>
     <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B726" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -9947,6 +13427,11 @@
       </c>
     </row>
     <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B727" t="inlineStr">
         <is>
           <t>Alvarado</t>
@@ -9960,9 +13445,14 @@
       </c>
     </row>
     <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Amatlán de los Reyes</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C728">
@@ -9973,6 +13463,11 @@
       </c>
     </row>
     <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B729" t="inlineStr">
         <is>
           <t>Atzacan</t>
@@ -9986,6 +13481,11 @@
       </c>
     </row>
     <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B730" t="inlineStr">
         <is>
           <t>Chalma</t>
@@ -9999,6 +13499,11 @@
       </c>
     </row>
     <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B731" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -10012,6 +13517,11 @@
       </c>
     </row>
     <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B732" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -10025,6 +13535,11 @@
       </c>
     </row>
     <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B733" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -10038,6 +13553,11 @@
       </c>
     </row>
     <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B734" t="inlineStr">
         <is>
           <t>Coxquihui</t>
@@ -10051,6 +13571,11 @@
       </c>
     </row>
     <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B735" t="inlineStr">
         <is>
           <t>Cuichapa</t>
@@ -10064,6 +13589,11 @@
       </c>
     </row>
     <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B736" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -10077,6 +13607,11 @@
       </c>
     </row>
     <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B737" t="inlineStr">
         <is>
           <t>Gutiérrez Zamora</t>
@@ -10090,6 +13625,11 @@
       </c>
     </row>
     <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B738" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -10103,9 +13643,14 @@
       </c>
     </row>
     <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C739">
@@ -10116,6 +13661,11 @@
       </c>
     </row>
     <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B740" t="inlineStr">
         <is>
           <t>Jalacingo</t>
@@ -10129,6 +13679,11 @@
       </c>
     </row>
     <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B741" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -10142,6 +13697,11 @@
       </c>
     </row>
     <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B742" t="inlineStr">
         <is>
           <t>Juan Rodríguez Clara</t>
@@ -10155,9 +13715,14 @@
       </c>
     </row>
     <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Juchique de Ferrer</t>
+          <t>Juchique De Ferrer</t>
         </is>
       </c>
       <c r="C743">
@@ -10168,6 +13733,11 @@
       </c>
     </row>
     <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B744" t="inlineStr">
         <is>
           <t>La Perla</t>
@@ -10181,6 +13751,11 @@
       </c>
     </row>
     <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B745" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -10194,9 +13769,14 @@
       </c>
     </row>
     <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Lerdo de Tejada</t>
+          <t>Lerdo De Tejada</t>
         </is>
       </c>
       <c r="C746">
@@ -10207,6 +13787,11 @@
       </c>
     </row>
     <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B747" t="inlineStr">
         <is>
           <t>Mariano Escobedo</t>
@@ -10220,9 +13805,14 @@
       </c>
     </row>
     <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C748">
@@ -10233,6 +13823,11 @@
       </c>
     </row>
     <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B749" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -10246,6 +13841,11 @@
       </c>
     </row>
     <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B750" t="inlineStr">
         <is>
           <t>Naolinco</t>
@@ -10259,6 +13859,11 @@
       </c>
     </row>
     <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B751" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -10272,6 +13877,11 @@
       </c>
     </row>
     <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B752" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -10285,6 +13895,11 @@
       </c>
     </row>
     <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B753" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -10298,9 +13913,14 @@
       </c>
     </row>
     <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Paso de Ovejas</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C754">
@@ -10311,6 +13931,11 @@
       </c>
     </row>
     <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B755" t="inlineStr">
         <is>
           <t>Perote</t>
@@ -10324,6 +13949,11 @@
       </c>
     </row>
     <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B756" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -10337,6 +13967,11 @@
       </c>
     </row>
     <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B757" t="inlineStr">
         <is>
           <t>Río Blanco</t>
@@ -10350,6 +13985,11 @@
       </c>
     </row>
     <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B758" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -10363,6 +14003,11 @@
       </c>
     </row>
     <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B759" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -10376,6 +14021,11 @@
       </c>
     </row>
     <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B760" t="inlineStr">
         <is>
           <t>Soledad Atzompa</t>
@@ -10389,9 +14039,14 @@
       </c>
     </row>
     <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Tatahuicapan de Juárez</t>
+          <t>Tatahuicapan De Juárez</t>
         </is>
       </c>
       <c r="C761">
@@ -10402,6 +14057,11 @@
       </c>
     </row>
     <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B762" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -10415,6 +14075,11 @@
       </c>
     </row>
     <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B763" t="inlineStr">
         <is>
           <t>Tihuatlán</t>
@@ -10428,6 +14093,11 @@
       </c>
     </row>
     <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B764" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -10441,6 +14111,11 @@
       </c>
     </row>
     <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B765" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -10454,6 +14129,11 @@
       </c>
     </row>
     <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B766" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -10467,9 +14147,14 @@
       </c>
     </row>
     <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Vega de Alatorre</t>
+          <t>Vega De Alatorre</t>
         </is>
       </c>
       <c r="C767">
@@ -10480,6 +14165,11 @@
       </c>
     </row>
     <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B768" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -10493,6 +14183,11 @@
       </c>
     </row>
     <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B769" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -10506,6 +14201,11 @@
       </c>
     </row>
     <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B770" t="inlineStr">
         <is>
           <t>Xoxocotla</t>
@@ -10519,6 +14219,11 @@
       </c>
     </row>
     <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B771" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -10532,6 +14237,11 @@
       </c>
     </row>
     <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B772" t="inlineStr">
         <is>
           <t>Total</t>
@@ -10563,6 +14273,11 @@
       </c>
     </row>
     <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B774" t="inlineStr">
         <is>
           <t>Total</t>
@@ -10594,6 +14309,11 @@
       </c>
     </row>
     <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B776" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -10607,6 +14327,11 @@
       </c>
     </row>
     <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B777" t="inlineStr">
         <is>
           <t>Calera</t>
@@ -10620,6 +14345,11 @@
       </c>
     </row>
     <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B778" t="inlineStr">
         <is>
           <t>Chalchihuites</t>
@@ -10633,6 +14363,11 @@
       </c>
     </row>
     <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B779" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -10646,6 +14381,11 @@
       </c>
     </row>
     <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B780" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -10659,6 +14399,11 @@
       </c>
     </row>
     <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B781" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -10672,6 +14417,11 @@
       </c>
     </row>
     <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B782" t="inlineStr">
         <is>
           <t>Jalpa</t>
@@ -10685,6 +14435,11 @@
       </c>
     </row>
     <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B783" t="inlineStr">
         <is>
           <t>Juchipila</t>
@@ -10698,6 +14453,11 @@
       </c>
     </row>
     <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B784" t="inlineStr">
         <is>
           <t>Loreto</t>
@@ -10711,6 +14471,11 @@
       </c>
     </row>
     <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B785" t="inlineStr">
         <is>
           <t>Luis Moya</t>
@@ -10724,9 +14489,14 @@
       </c>
     </row>
     <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>Mezquital del Oro</t>
+          <t>Mezquital Del Oro</t>
         </is>
       </c>
       <c r="C786">
@@ -10737,6 +14507,11 @@
       </c>
     </row>
     <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B787" t="inlineStr">
         <is>
           <t>Miguel Auza</t>
@@ -10750,6 +14525,11 @@
       </c>
     </row>
     <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B788" t="inlineStr">
         <is>
           <t>Momax</t>
@@ -10763,6 +14543,11 @@
       </c>
     </row>
     <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B789" t="inlineStr">
         <is>
           <t>Monte Escobedo</t>
@@ -10776,9 +14561,14 @@
       </c>
     </row>
     <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>Nochistlán de Mejía</t>
+          <t>Nochistlán De Mejía</t>
         </is>
       </c>
       <c r="C790">
@@ -10789,9 +14579,14 @@
       </c>
     </row>
     <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>Noria de Ángeles</t>
+          <t>Noria De Ángeles</t>
         </is>
       </c>
       <c r="C791">
@@ -10802,6 +14597,11 @@
       </c>
     </row>
     <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B792" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -10815,6 +14615,11 @@
       </c>
     </row>
     <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B793" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -10828,6 +14633,11 @@
       </c>
     </row>
     <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B794" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -10841,6 +14651,11 @@
       </c>
     </row>
     <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B795" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -10854,6 +14669,11 @@
       </c>
     </row>
     <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B796" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -10867,6 +14687,11 @@
       </c>
     </row>
     <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B797" t="inlineStr">
         <is>
           <t>Tabasco</t>
@@ -10880,6 +14705,11 @@
       </c>
     </row>
     <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B798" t="inlineStr">
         <is>
           <t>Tepechitlán</t>
@@ -10893,9 +14723,14 @@
       </c>
     </row>
     <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Teúl de González Ortega</t>
+          <t>Teúl De González Ortega</t>
         </is>
       </c>
       <c r="C799">
@@ -10906,9 +14741,14 @@
       </c>
     </row>
     <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C800">
@@ -10919,6 +14759,11 @@
       </c>
     </row>
     <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B801" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -10932,9 +14777,14 @@
       </c>
     </row>
     <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C802">
@@ -10945,6 +14795,11 @@
       </c>
     </row>
     <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B803" t="inlineStr">
         <is>
           <t>Villa García</t>
@@ -10958,6 +14813,11 @@
       </c>
     </row>
     <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B804" t="inlineStr">
         <is>
           <t>Villa González Ortega</t>
@@ -10971,6 +14831,11 @@
       </c>
     </row>
     <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B805" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -10984,6 +14849,11 @@
       </c>
     </row>
     <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B806" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -10997,6 +14867,11 @@
       </c>
     </row>
     <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B807" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -11010,6 +14885,11 @@
       </c>
     </row>
     <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B808" t="inlineStr">
         <is>
           <t>Total</t>
@@ -11033,41 +14913,6 @@
       </c>
       <c r="D809">
         <v>1</v>
-      </c>
-    </row>
-    <row r="811">
-      <c r="A811" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 701,861</t>
-        </is>
-      </c>
-    </row>
-    <row r="812">
-      <c r="A812" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="813">
-      <c r="A813" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="814">
-      <c r="A814" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="815">
-      <c r="A815" t="inlineStr">
-        <is>
-          <t>Mayo de 2022</t>
-        </is>
       </c>
     </row>
   </sheetData>
